--- a/PIMCO_GIS_Income_Tracker.xlsx
+++ b/PIMCO_GIS_Income_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
   <si>
     <t xml:space="preserve">PIMCO GIS Income Fund — Monthly Tracker</t>
   </si>
@@ -497,12 +497,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -642,6 +638,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -711,27 +708,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -843,6 +836,9 @@
                 <c:pt idx="2">
                   <c:v>16</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>15</c:v>
                 </c:pt>
@@ -860,6 +856,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>13</c:v>
@@ -908,27 +907,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1040,6 +1035,9 @@
                 <c:pt idx="2">
                   <c:v>34</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>34</c:v>
                 </c:pt>
@@ -1057,6 +1055,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>37</c:v>
@@ -1105,27 +1106,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1237,6 +1234,9 @@
                 <c:pt idx="2">
                   <c:v>15</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>17</c:v>
                 </c:pt>
@@ -1253,6 +1253,9 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -1302,27 +1305,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1434,6 +1433,9 @@
                 <c:pt idx="2">
                   <c:v>15</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>14</c:v>
                 </c:pt>
@@ -1450,6 +1452,9 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -1499,27 +1504,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1631,6 +1632,9 @@
                 <c:pt idx="2">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>5</c:v>
                 </c:pt>
@@ -1647,6 +1651,9 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -1696,27 +1703,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -1828,6 +1831,9 @@
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1844,6 +1850,9 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -1893,27 +1902,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2025,6 +2030,9 @@
                 <c:pt idx="2">
                   <c:v>5</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>6</c:v>
                 </c:pt>
@@ -2041,6 +2049,9 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -2090,27 +2101,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2222,6 +2229,9 @@
                 <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>8</c:v>
                 </c:pt>
@@ -2239,6 +2249,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11</c:v>
@@ -2287,27 +2300,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2419,6 +2428,9 @@
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2435,6 +2447,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -2462,11 +2477,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90213996"/>
-        <c:axId val="52052890"/>
+        <c:axId val="68235809"/>
+        <c:axId val="61592201"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90213996"/>
+        <c:axId val="68235809"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2505,7 +2520,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2532,7 +2547,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52052890"/>
+        <c:crossAx val="61592201"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2540,7 +2555,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52052890"/>
+        <c:axId val="61592201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2589,7 +2604,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2616,7 +2631,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90213996"/>
+        <c:crossAx val="68235809"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2675,6 +2690,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2744,27 +2760,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -2876,6 +2888,9 @@
                 <c:pt idx="2">
                   <c:v>3.96</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.42</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>5.13</c:v>
                 </c:pt>
@@ -2893,6 +2908,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>4.82</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.9</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>5.19</c:v>
@@ -2919,11 +2937,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="26110929"/>
-        <c:axId val="15310651"/>
+        <c:axId val="39560152"/>
+        <c:axId val="38442382"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="26110929"/>
+        <c:axId val="39560152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2962,7 +2980,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2989,7 +3007,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15310651"/>
+        <c:crossAx val="38442382"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2997,7 +3015,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15310651"/>
+        <c:axId val="38442382"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3046,7 +3064,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3073,7 +3091,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26110929"/>
+        <c:crossAx val="39560152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3132,6 +3150,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3201,27 +3220,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -3333,6 +3348,9 @@
                 <c:pt idx="2">
                   <c:v>7.24</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.9</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>6.55</c:v>
                 </c:pt>
@@ -3350,6 +3368,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6.07</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>6.29</c:v>
@@ -3398,27 +3419,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -3530,6 +3547,9 @@
                 <c:pt idx="2">
                   <c:v>3.02</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.83</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>4.86</c:v>
                 </c:pt>
@@ -3547,6 +3567,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.23</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.54</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0.51</c:v>
@@ -3573,11 +3596,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="16751510"/>
-        <c:axId val="79145190"/>
+        <c:axId val="54400581"/>
+        <c:axId val="94232581"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="16751510"/>
+        <c:axId val="54400581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3616,7 +3639,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3643,7 +3666,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79145190"/>
+        <c:crossAx val="94232581"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3651,7 +3674,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79145190"/>
+        <c:axId val="94232581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3700,7 +3723,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3727,7 +3750,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16751510"/>
+        <c:crossAx val="54400581"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3786,6 +3809,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3855,27 +3879,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -3987,6 +4007,9 @@
                 <c:pt idx="2">
                   <c:v>64</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>15</c:v>
                 </c:pt>
@@ -4004,6 +4027,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>16</c:v>
@@ -4052,27 +4078,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4184,6 +4206,9 @@
                 <c:pt idx="2">
                   <c:v>8</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>58</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>57</c:v>
                 </c:pt>
@@ -4201,6 +4226,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>59</c:v>
@@ -4249,27 +4277,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4381,6 +4405,9 @@
                 <c:pt idx="2">
                   <c:v>7</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>6</c:v>
                 </c:pt>
@@ -4397,6 +4424,9 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -4446,27 +4476,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4578,6 +4604,9 @@
                 <c:pt idx="2">
                   <c:v>10</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>9</c:v>
                 </c:pt>
@@ -4594,6 +4623,9 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -4643,27 +4675,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4775,6 +4803,9 @@
                 <c:pt idx="2">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>4</c:v>
                 </c:pt>
@@ -4791,6 +4822,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -4840,27 +4874,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -4972,6 +5002,9 @@
                 <c:pt idx="2">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>2</c:v>
                 </c:pt>
@@ -4988,6 +5021,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -5037,27 +5073,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -5169,6 +5201,9 @@
                 <c:pt idx="2">
                   <c:v>4</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>4</c:v>
                 </c:pt>
@@ -5185,6 +5220,9 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -5234,27 +5272,23 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
@@ -5366,6 +5400,9 @@
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>2</c:v>
                 </c:pt>
@@ -5382,6 +5419,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
@@ -5409,11 +5449,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="93149518"/>
-        <c:axId val="72706960"/>
+        <c:axId val="52048288"/>
+        <c:axId val="46238633"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="93149518"/>
+        <c:axId val="52048288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5452,7 +5492,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5479,7 +5519,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72706960"/>
+        <c:crossAx val="46238633"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5487,7 +5527,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72706960"/>
+        <c:axId val="46238633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5536,7 +5576,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5563,7 +5603,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93149518"/>
+        <c:crossAx val="52048288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6493,9 +6533,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>78480</xdr:colOff>
+      <xdr:colOff>78840</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>133560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6504,7 +6544,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="10409040" y="628560"/>
-        <a:ext cx="8639280" cy="3419280"/>
+        <a:ext cx="8639640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6528,9 +6568,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>364320</xdr:colOff>
+      <xdr:colOff>364680</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>164520</xdr:rowOff>
+      <xdr:rowOff>164880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6539,7 +6579,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5686560" y="628560"/>
-        <a:ext cx="6479280" cy="2879280"/>
+        <a:ext cx="6479640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6558,9 +6598,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>364320</xdr:colOff>
+      <xdr:colOff>364680</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>22320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6569,7 +6609,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5686560" y="4105440"/>
-        <a:ext cx="6479280" cy="2879280"/>
+        <a:ext cx="6479640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6593,9 +6633,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>78120</xdr:colOff>
+      <xdr:colOff>78480</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>133560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6604,7 +6644,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8223840" y="628560"/>
-        <a:ext cx="8639280" cy="3419280"/>
+        <a:ext cx="8639640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6800,157 +6840,157 @@
   <dimension ref="B1:C27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+      <c r="C15" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="8"/>
+      <c r="C27" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6976,737 +7016,773 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="13" t="n">
+      <c r="I4" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="J4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="14" t="n">
+      <c r="K4" s="13" t="n">
         <f aca="false">IF(COUNT(B4:J4)=0,"",SUM(B4:J4))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="13" t="n">
         <f aca="false">IF(COUNT(B5:J5)=0,"",SUM(B5:J5))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="K6" s="13" t="n">
         <f aca="false">IF(COUNT(B6:J6)=0,"",SUM(B6:J6))</f>
         <v>98</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14" t="str">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13" t="str">
         <f aca="false">IF(COUNT(B7:J7)=0,"",SUM(B7:J7))</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14" t="str">
+      <c r="B8" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="13" t="n">
         <f aca="false">IF(COUNT(B8:J8)=0,"",SUM(B8:J8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="13" t="n">
         <f aca="false">IF(COUNT(B9:J9)=0,"",SUM(B9:J9))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="13" t="n">
         <f aca="false">IF(COUNT(B10:J10)=0,"",SUM(B10:J10))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="J11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="13" t="n">
         <f aca="false">IF(COUNT(B11:J11)=0,"",SUM(B11:J11))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="13" t="n">
         <f aca="false">IF(COUNT(B12:J12)=0,"",SUM(B12:J12))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="13" t="n">
         <f aca="false">IF(COUNT(B13:J13)=0,"",SUM(B13:J13))</f>
         <v>101</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="13" t="n">
         <f aca="false">IF(COUNT(B14:J14)=0,"",SUM(B14:J14))</f>
         <v>101</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14" t="str">
+      <c r="B15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="13" t="n">
         <f aca="false">IF(COUNT(B15:J15)=0,"",SUM(B15:J15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="13" t="n">
         <f aca="false">IF(COUNT(B16:J16)=0,"",SUM(B16:J16))</f>
         <v>98</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="13" t="n">
         <f aca="false">IF(COUNT(B17:J17)=0,"",SUM(B17:J17))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="14" t="n">
+      <c r="K18" s="13" t="n">
         <f aca="false">IF(COUNT(B18:J18)=0,"",SUM(B18:J18))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="13" t="n">
         <f aca="false">IF(COUNT(B19:J19)=0,"",SUM(B19:J19))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="14" t="str">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="13" t="str">
         <f aca="false">IF(COUNT(B20:J20)=0,"",SUM(B20:J20))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="14" t="str">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="13" t="str">
         <f aca="false">IF(COUNT(B21:J21)=0,"",SUM(B21:J21))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="14" t="str">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="13" t="str">
         <f aca="false">IF(COUNT(B22:J22)=0,"",SUM(B22:J22))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14" t="str">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="13" t="str">
         <f aca="false">IF(COUNT(B23:J23)=0,"",SUM(B23:J23))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14" t="str">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="13" t="str">
         <f aca="false">IF(COUNT(B24:J24)=0,"",SUM(B24:J24))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="14" t="str">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="13" t="str">
         <f aca="false">IF(COUNT(B25:J25)=0,"",SUM(B25:J25))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="14" t="str">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="13" t="str">
         <f aca="false">IF(COUNT(B26:J26)=0,"",SUM(B26:J26))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14" t="str">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="13" t="str">
         <f aca="false">IF(COUNT(B27:J27)=0,"",SUM(B27:J27))</f>
         <v/>
       </c>
@@ -7735,367 +7811,383 @@
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="14" t="n">
         <v>4.61</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="14" t="n">
         <v>7.25</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="14" t="n">
         <v>3.99</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="14" t="n">
         <v>6.98</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="14" t="n">
         <v>2.83</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="14" t="n">
         <v>3.96</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="14" t="n">
         <v>7.24</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>3.02</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="B8" s="14" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="14" t="n">
         <v>5.13</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="14" t="n">
         <v>6.55</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="14" t="n">
         <v>4.86</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="14" t="n">
         <v>5.38</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="14" t="n">
         <v>6.51</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="14" t="n">
         <v>4.86</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="14" t="n">
         <v>5.25</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="14" t="n">
         <v>6.31</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="14" t="n">
         <v>6.46</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="14" t="n">
         <v>5.21</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="14" t="n">
         <v>6.25</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="14" t="n">
         <v>7.26</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="14" t="n">
         <v>4.98</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="14" t="n">
         <v>6.11</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="14" t="n">
         <v>8.49</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="14" t="n">
         <v>4.82</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="14" t="n">
         <v>6.07</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="14" t="n">
         <v>9.23</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="B15" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>9.54</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="14" t="n">
         <v>5.19</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="14" t="n">
         <v>6.29</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="14" t="n">
         <v>0.51</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="14" t="n">
         <v>5.15</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="14" t="n">
         <v>6.05</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="14" t="n">
         <v>1.57</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="14" t="n">
         <v>6.25</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="14" t="n">
         <v>6.9</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="14" t="n">
         <v>-0.96</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="14" t="n">
         <v>6.29</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="14" t="n">
         <v>-0.11</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8121,682 +8213,714 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="13" t="n">
+      <c r="I4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="14" t="n">
+      <c r="J4" s="13" t="n">
         <f aca="false">IF(COUNT(B4:I4)=0,"",SUM(B4:I4))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="13" t="n">
         <f aca="false">IF(COUNT(B5:I5)=0,"",SUM(B5:I5))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="13" t="n">
         <f aca="false">IF(COUNT(B6:I6)=0,"",SUM(B6:I6))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14" t="str">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13" t="str">
         <f aca="false">IF(COUNT(B7:I7)=0,"",SUM(B7:I7))</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="14" t="str">
+      <c r="B8" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="13" t="n">
         <f aca="false">IF(COUNT(B8:I8)=0,"",SUM(B8:I8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="13" t="n">
         <f aca="false">IF(COUNT(B9:I9)=0,"",SUM(B9:I9))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="13" t="n">
         <f aca="false">IF(COUNT(B10:I10)=0,"",SUM(B10:I10))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="13" t="n">
         <f aca="false">IF(COUNT(B11:I11)=0,"",SUM(B11:I11))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="13" t="n">
         <f aca="false">IF(COUNT(B12:I12)=0,"",SUM(B12:I12))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="13" t="n">
         <f aca="false">IF(COUNT(B13:I13)=0,"",SUM(B13:I13))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="I14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="13" t="n">
         <f aca="false">IF(COUNT(B14:I14)=0,"",SUM(B14:I14))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14" t="str">
+      <c r="B15" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="13" t="n">
         <f aca="false">IF(COUNT(B15:I15)=0,"",SUM(B15:I15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="13" t="n">
         <f aca="false">IF(COUNT(B16:I16)=0,"",SUM(B16:I16))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="13" t="n">
         <f aca="false">IF(COUNT(B17:I17)=0,"",SUM(B17:I17))</f>
         <v>99</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="I18" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="J18" s="13" t="n">
         <f aca="false">IF(COUNT(B18:I18)=0,"",SUM(B18:I18))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="13" t="n">
         <f aca="false">IF(COUNT(B19:I19)=0,"",SUM(B19:I19))</f>
         <v>100</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14" t="str">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13" t="str">
         <f aca="false">IF(COUNT(B20:I20)=0,"",SUM(B20:I20))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="14" t="str">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13" t="str">
         <f aca="false">IF(COUNT(B21:I21)=0,"",SUM(B21:I21))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="14" t="str">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13" t="str">
         <f aca="false">IF(COUNT(B22:I22)=0,"",SUM(B22:I22))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="14" t="str">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="13" t="str">
         <f aca="false">IF(COUNT(B23:I23)=0,"",SUM(B23:I23))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="14" t="str">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="13" t="str">
         <f aca="false">IF(COUNT(B24:I24)=0,"",SUM(B24:I24))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="14" t="str">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="13" t="str">
         <f aca="false">IF(COUNT(B25:I25)=0,"",SUM(B25:I25))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="14" t="str">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="13" t="str">
         <f aca="false">IF(COUNT(B26:I26)=0,"",SUM(B26:I26))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="14" t="str">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13" t="str">
         <f aca="false">IF(COUNT(B27:I27)=0,"",SUM(B27:I27))</f>
         <v/>
       </c>

--- a/PIMCO_GIS_Income_Tracker.xlsx
+++ b/PIMCO_GIS_Income_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
   <si>
     <t xml:space="preserve">PIMCO GIS Income Fund — Monthly Tracker</t>
   </si>
@@ -872,6 +872,9 @@
                 <c:pt idx="15">
                   <c:v>14</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>14</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1071,6 +1074,9 @@
                 <c:pt idx="15">
                   <c:v>36</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>36</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1270,6 +1276,9 @@
                 <c:pt idx="15">
                   <c:v>14</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>14</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1469,6 +1478,9 @@
                 <c:pt idx="15">
                   <c:v>14</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>15</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1668,6 +1680,9 @@
                 <c:pt idx="15">
                   <c:v>5</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1867,6 +1882,9 @@
                 <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2066,6 +2084,9 @@
                 <c:pt idx="15">
                   <c:v>7</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2265,6 +2286,9 @@
                 <c:pt idx="15">
                   <c:v>9</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2464,6 +2488,9 @@
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2477,11 +2504,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68235809"/>
-        <c:axId val="61592201"/>
+        <c:axId val="58825325"/>
+        <c:axId val="78311650"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68235809"/>
+        <c:axId val="58825325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2547,7 +2574,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61592201"/>
+        <c:crossAx val="78311650"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2555,7 +2582,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61592201"/>
+        <c:axId val="78311650"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2631,7 +2658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68235809"/>
+        <c:crossAx val="58825325"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2924,6 +2951,9 @@
                 <c:pt idx="15">
                   <c:v>6.29</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.31</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2937,11 +2967,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="39560152"/>
-        <c:axId val="38442382"/>
+        <c:axId val="9319301"/>
+        <c:axId val="35617805"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39560152"/>
+        <c:axId val="9319301"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3007,7 +3037,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38442382"/>
+        <c:crossAx val="35617805"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3015,7 +3045,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38442382"/>
+        <c:axId val="35617805"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3091,7 +3121,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39560152"/>
+        <c:crossAx val="9319301"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3384,6 +3414,9 @@
                 <c:pt idx="15">
                   <c:v>7</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.83</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3583,6 +3616,9 @@
                 <c:pt idx="15">
                   <c:v>-0.11</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.51</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3596,11 +3632,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="54400581"/>
-        <c:axId val="94232581"/>
+        <c:axId val="29950653"/>
+        <c:axId val="7805261"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54400581"/>
+        <c:axId val="29950653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3666,7 +3702,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94232581"/>
+        <c:crossAx val="7805261"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3674,7 +3710,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94232581"/>
+        <c:axId val="7805261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3750,7 +3786,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54400581"/>
+        <c:crossAx val="29950653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4043,6 +4079,9 @@
                 <c:pt idx="15">
                   <c:v>14</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>12</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4242,6 +4281,9 @@
                 <c:pt idx="15">
                   <c:v>58</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>59</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4441,6 +4483,9 @@
                 <c:pt idx="15">
                   <c:v>7</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4640,6 +4685,9 @@
                 <c:pt idx="15">
                   <c:v>9</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4839,6 +4887,9 @@
                 <c:pt idx="15">
                   <c:v>6</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5038,6 +5089,9 @@
                 <c:pt idx="15">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5237,6 +5291,9 @@
                 <c:pt idx="15">
                   <c:v>3</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5436,6 +5493,9 @@
                 <c:pt idx="15">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5449,11 +5509,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52048288"/>
-        <c:axId val="46238633"/>
+        <c:axId val="39708201"/>
+        <c:axId val="8418526"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52048288"/>
+        <c:axId val="39708201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5519,7 +5579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46238633"/>
+        <c:crossAx val="8418526"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5527,7 +5587,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46238633"/>
+        <c:axId val="8418526"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5603,7 +5663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52048288"/>
+        <c:crossAx val="39708201"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7647,18 +7707,36 @@
       <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="13" t="str">
+      <c r="B20" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="n">
         <f aca="false">IF(COUNT(B20:J20)=0,"",SUM(B20:J20))</f>
-        <v/>
+        <v>99</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8121,10 +8199,18 @@
       <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+      <c r="B20" s="14" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -8793,17 +8879,33 @@
       <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="13" t="str">
+      <c r="B20" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="13" t="n">
         <f aca="false">IF(COUNT(B20:I20)=0,"",SUM(B20:I20))</f>
-        <v/>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
